--- a/Compititor's_Price/Novia_Prices/Novia_Prices_29-10-2026.xlsx
+++ b/Compititor's_Price/Novia_Prices/Novia_Prices_29-10-2026.xlsx
@@ -599,7 +599,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>£124.19</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -1376,7 +1376,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>£91.38</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1450,7 +1450,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>£65.5</t>
+          <t>Error</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1487,7 +1487,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>£137.24</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1561,7 +1561,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>£124.94</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
